--- a/artfynd/A 43709-2025 artfynd.xlsx
+++ b/artfynd/A 43709-2025 artfynd.xlsx
@@ -675,46 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80073872</v>
+        <v>80073659</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57959</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100046</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitryggig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dendrocopos leucotos</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1803)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -727,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>801428.0446294483</v>
+        <v>801428</v>
       </c>
       <c r="R2" t="n">
-        <v>7329376.509020807</v>
+        <v>7329377</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -762,7 +761,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +771,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Sågs 2-3 minuter när den besökte några döda granar på ett litet område som eldhärjades för ett par år sedan. Som närmast var den blott 10-15 m ifrån mig. Fågeln lät höra av sig flera gånger samtidigt som den bytte träd några gånger och försvann slutligen i sydlig riktning. Fågeln eftersöktes en dryg halvtimma utan resultat.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,39 +796,34 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mats Bergquist, Roger Nordmark, Per Nyström</t>
+          <t>Mats Bergquist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80701988</v>
+        <v>80073872</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,15 +833,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -855,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>801428.0446294483</v>
+        <v>801428</v>
       </c>
       <c r="R3" t="n">
-        <v>7329376.509020807</v>
+        <v>7329377</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -885,27 +880,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-11-02</t>
+          <t>2019-09-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-11-02</t>
+          <t>2019-09-24</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Letade mat i ett flertal brända granar.</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,22 +915,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mats Bergquist</t>
+          <t>Mats Bergquist, Roger Nordmark, Per Nyström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80897295</v>
+        <v>80701988</v>
       </c>
       <c r="B4" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,30 +933,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -984,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>801428.0446294483</v>
+        <v>801428</v>
       </c>
       <c r="R4" t="n">
-        <v>7329376.509020807</v>
+        <v>7329377</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1014,22 +1003,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-11-17</t>
+          <t>2019-11-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-11-17</t>
+          <t>2019-11-02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Letade mat i ett flertal brända granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,50 +1050,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80073659</v>
+        <v>80897295</v>
       </c>
       <c r="B5" t="n">
-        <v>56407</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på raritetsblankett</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100046</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitryggig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dendrocopos leucotos</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1803)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1112,10 +1097,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>801428.0446294483</v>
+        <v>801428</v>
       </c>
       <c r="R5" t="n">
-        <v>7329376.509020807</v>
+        <v>7329377</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1142,27 +1127,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-09-24</t>
+          <t>2019-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-09-24</t>
+          <t>2019-11-17</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Sågs 2-3 minuter när den besökte några döda granar på ett litet område som eldhärjades för ett par år sedan. Som närmast var den blott 10-15 m ifrån mig. Fågeln lät höra av sig flera gånger samtidigt som den bytte träd några gånger och försvann slutligen i sydlig riktning. Fågeln eftersöktes en dryg halvtimma utan resultat.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1192,12 +1172,7 @@
         <v>88175497</v>
       </c>
       <c r="B6" t="n">
-        <v>8367</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>801428.0446294483</v>
+        <v>801428</v>
       </c>
       <c r="R6" t="n">
-        <v>7329376.509020807</v>
+        <v>7329377</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 43709-2025 artfynd.xlsx
+++ b/artfynd/A 43709-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -800,6 +805,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80073659</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -919,6 +929,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80073872</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,6 +1062,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80701988</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1166,6 +1186,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80897295</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1288,8 +1313,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88175497</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>